--- a/data/nzd0583/nzd0583.xlsx
+++ b/data/nzd0583/nzd0583.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M270"/>
+  <dimension ref="A1:M272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12372,7 +12372,7 @@
         <v>211.21</v>
       </c>
       <c r="F269" t="n">
-        <v>249.61</v>
+        <v>214.28</v>
       </c>
       <c r="G269" t="n">
         <v>217.75</v>
@@ -12408,22 +12408,22 @@
         <v>278.76</v>
       </c>
       <c r="C270" t="n">
-        <v>297.6</v>
+        <v>229.41</v>
       </c>
       <c r="D270" t="n">
-        <v>284.09</v>
+        <v>222.34</v>
       </c>
       <c r="E270" t="n">
         <v>206.39</v>
       </c>
       <c r="F270" t="n">
-        <v>279.12</v>
+        <v>211.21</v>
       </c>
       <c r="G270" t="n">
-        <v>244.93</v>
+        <v>217.75</v>
       </c>
       <c r="H270" t="n">
-        <v>243.55</v>
+        <v>214.33</v>
       </c>
       <c r="I270" t="n">
         <v>229.79</v>
@@ -12438,6 +12438,96 @@
         <v>219.64</v>
       </c>
       <c r="M270" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>278.76</v>
+      </c>
+      <c r="C271" t="n">
+        <v>202.23</v>
+      </c>
+      <c r="D271" t="n">
+        <v>200.57</v>
+      </c>
+      <c r="E271" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="F271" t="n">
+        <v>211.21</v>
+      </c>
+      <c r="G271" t="n">
+        <v>217.75</v>
+      </c>
+      <c r="H271" t="n">
+        <v>214.33</v>
+      </c>
+      <c r="I271" t="n">
+        <v>229.79</v>
+      </c>
+      <c r="J271" t="n">
+        <v>221.16</v>
+      </c>
+      <c r="K271" t="n">
+        <v>222.64</v>
+      </c>
+      <c r="L271" t="n">
+        <v>219.64</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>278.76</v>
+      </c>
+      <c r="C272" t="n">
+        <v>197.54</v>
+      </c>
+      <c r="D272" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="E272" t="n">
+        <v>198</v>
+      </c>
+      <c r="F272" t="n">
+        <v>202.65</v>
+      </c>
+      <c r="G272" t="n">
+        <v>213.75</v>
+      </c>
+      <c r="H272" t="n">
+        <v>211.65</v>
+      </c>
+      <c r="I272" t="n">
+        <v>230.92</v>
+      </c>
+      <c r="J272" t="n">
+        <v>222.68</v>
+      </c>
+      <c r="K272" t="n">
+        <v>224.77</v>
+      </c>
+      <c r="L272" t="n">
+        <v>222.48</v>
+      </c>
+      <c r="M272" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12454,7 +12544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B286"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15317,6 +15407,26 @@
       </c>
       <c r="B286" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -15479,28 +15589,28 @@
         <v>0.0286</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006100940865207741</v>
+        <v>0.09182399712688627</v>
       </c>
       <c r="J2" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K2" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L2" t="n">
-        <v>3.419763443202051e-06</v>
+        <v>0.0007552619088020407</v>
       </c>
       <c r="M2" t="n">
-        <v>19.00739861903742</v>
+        <v>19.3046505298612</v>
       </c>
       <c r="N2" t="n">
-        <v>586.670311169969</v>
+        <v>606.3778514176171</v>
       </c>
       <c r="O2" t="n">
-        <v>24.22127806640205</v>
+        <v>24.62474063655528</v>
       </c>
       <c r="P2" t="n">
-        <v>222.2461331365406</v>
+        <v>221.2759038535505</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15551,28 +15661,28 @@
         <v>0.0306</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.105003822281523</v>
+        <v>-4.15330940189564</v>
       </c>
       <c r="J3" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K3" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2553984483837693</v>
+        <v>0.266160751258665</v>
       </c>
       <c r="M3" t="n">
-        <v>37.97326096889326</v>
+        <v>37.52326945557841</v>
       </c>
       <c r="N3" t="n">
-        <v>2548.244469072882</v>
+        <v>2488.335838798368</v>
       </c>
       <c r="O3" t="n">
-        <v>50.48013935274825</v>
+        <v>49.88322201701057</v>
       </c>
       <c r="P3" t="n">
-        <v>306.446560961403</v>
+        <v>307.0081179047161</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15623,28 +15733,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.633659435302342</v>
+        <v>-1.690199463675936</v>
       </c>
       <c r="J4" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K4" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09265297788141835</v>
+        <v>0.1012250716673881</v>
       </c>
       <c r="M4" t="n">
-        <v>23.19474702187828</v>
+        <v>22.97514643685265</v>
       </c>
       <c r="N4" t="n">
-        <v>1538.229165661371</v>
+        <v>1504.993543830861</v>
       </c>
       <c r="O4" t="n">
-        <v>39.22026473216837</v>
+        <v>38.79424627223553</v>
       </c>
       <c r="P4" t="n">
-        <v>251.3129341061002</v>
+        <v>251.91317543623</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15695,28 +15805,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2961262716790332</v>
+        <v>-0.3116070510087772</v>
       </c>
       <c r="J5" t="n">
+        <v>271</v>
+      </c>
+      <c r="K5" t="n">
         <v>269</v>
       </c>
-      <c r="K5" t="n">
-        <v>267</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.03811958895953571</v>
+        <v>0.04239562756299986</v>
       </c>
       <c r="M5" t="n">
-        <v>9.351832579153651</v>
+        <v>9.368358952494809</v>
       </c>
       <c r="N5" t="n">
-        <v>127.1408677513562</v>
+        <v>127.0977287647015</v>
       </c>
       <c r="O5" t="n">
-        <v>11.27567593323594</v>
+        <v>11.27376284852141</v>
       </c>
       <c r="P5" t="n">
-        <v>219.2236050540885</v>
+        <v>219.3894133366274</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15767,28 +15877,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08602016571678242</v>
+        <v>0.004511256318032306</v>
       </c>
       <c r="J6" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K6" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008562487920294459</v>
+        <v>4.193158099863314e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.345041411066274</v>
+        <v>3.878993771021972</v>
       </c>
       <c r="N6" t="n">
-        <v>49.62582844760609</v>
+        <v>28.35113658794728</v>
       </c>
       <c r="O6" t="n">
-        <v>7.044560202568085</v>
+        <v>5.324578536179862</v>
       </c>
       <c r="P6" t="n">
-        <v>211.1469868023493</v>
+        <v>212.0114599569731</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15839,28 +15949,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2805817753125925</v>
+        <v>-0.2990840887480324</v>
       </c>
       <c r="J7" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K7" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09006729712953199</v>
+        <v>0.1094694420243899</v>
       </c>
       <c r="M7" t="n">
-        <v>5.085490254181369</v>
+        <v>4.985010071370837</v>
       </c>
       <c r="N7" t="n">
-        <v>46.61390068431349</v>
+        <v>43.00467819682287</v>
       </c>
       <c r="O7" t="n">
-        <v>6.827437343858491</v>
+        <v>6.557795223764072</v>
       </c>
       <c r="P7" t="n">
-        <v>222.9468246368982</v>
+        <v>223.1422621299161</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15911,28 +16021,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7758992268103005</v>
+        <v>-0.8091936091302828</v>
       </c>
       <c r="J8" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K8" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2201115533962277</v>
+        <v>0.2391574739060628</v>
       </c>
       <c r="M8" t="n">
-        <v>8.93178099569926</v>
+        <v>8.853463794151427</v>
       </c>
       <c r="N8" t="n">
-        <v>125.4628928488085</v>
+        <v>123.5510610960067</v>
       </c>
       <c r="O8" t="n">
-        <v>11.20102195555426</v>
+        <v>11.11535249535554</v>
       </c>
       <c r="P8" t="n">
-        <v>243.0294894918389</v>
+        <v>243.3809196001396</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15983,28 +16093,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7564002735115117</v>
+        <v>-0.7662439017740877</v>
       </c>
       <c r="J9" t="n">
+        <v>271</v>
+      </c>
+      <c r="K9" t="n">
         <v>269</v>
       </c>
-      <c r="K9" t="n">
-        <v>267</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.3095613900844296</v>
+        <v>0.3175116450116198</v>
       </c>
       <c r="M9" t="n">
-        <v>6.251249559471832</v>
+        <v>6.258662797705991</v>
       </c>
       <c r="N9" t="n">
-        <v>74.1125634889315</v>
+        <v>73.91786323490331</v>
       </c>
       <c r="O9" t="n">
-        <v>8.608865400790716</v>
+        <v>8.597549839047362</v>
       </c>
       <c r="P9" t="n">
-        <v>257.7693579369158</v>
+        <v>257.8740422288128</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16055,28 +16165,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4439247256242683</v>
+        <v>-0.4570836546236362</v>
       </c>
       <c r="J10" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K10" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4456621938318487</v>
+        <v>0.4531728517218918</v>
       </c>
       <c r="M10" t="n">
-        <v>2.931854518662424</v>
+        <v>2.980485438893203</v>
       </c>
       <c r="N10" t="n">
-        <v>14.19806695481087</v>
+        <v>14.72693878625985</v>
       </c>
       <c r="O10" t="n">
-        <v>3.768032239088577</v>
+        <v>3.837569385204632</v>
       </c>
       <c r="P10" t="n">
-        <v>243.2409809031432</v>
+        <v>243.3809991727612</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -16127,28 +16237,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3300508635433956</v>
+        <v>-0.3403051866448502</v>
       </c>
       <c r="J11" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K11" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1374788092612205</v>
+        <v>0.1456470839863399</v>
       </c>
       <c r="M11" t="n">
-        <v>4.267987700743672</v>
+        <v>4.279436576223048</v>
       </c>
       <c r="N11" t="n">
-        <v>39.58563388187604</v>
+        <v>39.68328032231379</v>
       </c>
       <c r="O11" t="n">
-        <v>6.291711522461598</v>
+        <v>6.299466669672425</v>
       </c>
       <c r="P11" t="n">
-        <v>239.8883143497441</v>
+        <v>239.9974225797305</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -16199,28 +16309,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.053869256025384</v>
+        <v>-1.093986842224647</v>
       </c>
       <c r="J12" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K12" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1193041333662804</v>
+        <v>0.1277780720326547</v>
       </c>
       <c r="M12" t="n">
-        <v>17.29439391992303</v>
+        <v>17.3749486760929</v>
       </c>
       <c r="N12" t="n">
-        <v>473.8573447973101</v>
+        <v>476.1759017119114</v>
       </c>
       <c r="O12" t="n">
-        <v>21.76826462530511</v>
+        <v>21.82145507778781</v>
       </c>
       <c r="P12" t="n">
-        <v>277.8357357355132</v>
+        <v>278.2642203325224</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -16258,7 +16368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M270"/>
+  <dimension ref="A1:M272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33925,7 +34035,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>-46.62811605323408,169.13834500532488</t>
+          <t>-46.62837190096572,169.13807183591507</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -33977,12 +34087,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-46.62904825359737,169.14123888448827</t>
+          <t>-46.629541746502085,169.14071100877118</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>-46.628719611757695,169.14029365377428</t>
+          <t>-46.62916649423829,169.13981562763897</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -33992,17 +34102,17 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>-46.62790235137716,169.13857317284464</t>
+          <t>-46.62839413281687,169.13804809873844</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>-46.62772354099215,169.1374682720401</t>
+          <t>-46.627920349007816,169.1372580799459</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>-46.62736539667954,169.1369871989397</t>
+          <t>-46.627469656544186,169.13663723003594</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -34026,6 +34136,140 @@
         </is>
       </c>
       <c r="M270" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>-46.629611008265584,169.1419337012174</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>-46.62973844813909,169.14050059892756</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>-46.62932404238792,169.13964709732915</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>-46.62888240710421,169.13882269152415</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-46.62839413281687,169.13804809873844</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-46.627920349007816,169.1372580799459</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-46.627469656544186,169.13663723003594</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-46.62675441341588,169.13640779517456</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-46.62612515132417,169.13588986255346</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-46.62545990892607,169.13549308481714</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-46.62481051128717,169.1350425745286</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>-46.629611008265584,169.1419337012174</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>-46.62977238962072,169.1404642918479</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>-46.62936073362532,169.13960784828112</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-46.62891622582468,169.13878658326584</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-46.62845612127133,169.1379819128908</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-46.62794931262288,169.13722714646804</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-46.62747921899477,169.1366051315229</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-46.62675037962028,169.13642132789505</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-46.6261197227902,169.1359080640436</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-46.62545230914191,169.1355185951212</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-46.624800368728074,169.13507658187507</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
